--- a/dataset/Faulty/st_underrun.xlsx
+++ b/dataset/Faulty/st_underrun.xlsx
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/st_underrun.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/st_underrun.c</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -456,14 +456,14 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/st_underrun.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/st_underrun.c</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -478,14 +478,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/st_underrun.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/st_underrun.c</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -495,19 +495,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>typedef struct { char buf[10]; char buf1[10]; char buf2[10]; char buf3[10]; char buf4[10]; } st_underrun_003_s_001; extern volatile int vflag; void st_underrun_003 () { st_underrun_003_s_001 s; st_underrun_003_func_001(&amp;s); st_underrun_003_func_002(&amp;s); } void st_underrun_003_func_001 (st_underrun_003_s_001 *s) { char buf[10] = "STRING"; strcpy(s-&gt;buf,buf); } void st_underrun_003_func_002 (st_underrun_003_s_001 *s) { int len = strlen(s-&gt;buf) - 1; do { s-&gt;buf[len] = 'A'; len--; /* if (s-&gt;buf[len] == '\0') break; */ }while (s-&gt;buf[len] != 'Z');/*Tool should detect this line as error*/ /* Stack Under RUN error */ }</t>
+          <t>typedef struct { char buf[10]; char buf1[10]; char buf2[10]; char buf3[10]; char buf4[10]; } st_underrun_003_s_001; extern volatile int vflag; void st_underrun_003 () { st_underrun_003_s_001 s; st_underrun_003_func_001(&amp;s); st_underrun_003_func_002(&amp;s); } void st_underrun_003_func_002 (st_underrun_003_s_001 *s) { int len = strlen(s-&gt;buf) - 1; do { s-&gt;buf[len] = 'A'; len--; /* if (s-&gt;buf[len] == '\0') break; */ }while (s-&gt;buf[len] != 'Z');/*Tool should detect this line as error*/ /* Stack Under RUN error */ } void st_underrun_003_func_001 (st_underrun_003_s_001 *s) { char buf[10] = "STRING"; strcpy(s-&gt;buf,buf); }</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/st_underrun.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/st_underrun.c</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -522,14 +522,14 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/st_underrun.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/st_underrun.c</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/st_underrun.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/st_underrun.c</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -566,14 +566,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/st_underrun.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/st_underrun.c</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -583,12 +583,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>typedef struct { char buf[10]; char buf1[10]; char buf2[10]; char buf3[10]; char buf4[10]; char buf5[10]; } st_underrun_007_s_001; extern volatile int vflag; void st_underrun_007 () { int flag = 0; st_underrun_007_s_001 s; s.buf[0] = 1; if (flag &gt;1 ) { st_underrun_007_func_002(s); } else { st_underrun_007_func_001(&amp;s); } } void st_underrun_007_func_001 (st_underrun_007_s_001 *s) { int len = strlen(s-&gt;buf) - 1; char c; for (;s-&gt;buf[len] != 'Z';len--) { c = s-&gt;buf[len]; /*Tool should detect this line as error*/ /* Stack Under RUN error */ /*if (s-&gt;buf[len] == '\0') break;*/ } } void st_underrun_007_func_002 (st_underrun_007_s_001 s) { s.buf[0] = 1; }</t>
+          <t>typedef struct { char buf[10]; char buf1[10]; char buf2[10]; char buf3[10]; char buf4[10]; char buf5[10]; } st_underrun_007_s_001; extern volatile int vflag; void st_underrun_007 () { int flag = 0; st_underrun_007_s_001 s; s.buf[0] = 1; if (flag &gt;1 ) { st_underrun_007_func_002(s); } else { st_underrun_007_func_001(&amp;s); } } void st_underrun_007_func_002 (st_underrun_007_s_001 s) { s.buf[0] = 1; } void st_underrun_007_func_001 (st_underrun_007_s_001 *s) { int len = strlen(s-&gt;buf) - 1; char c; for (;s-&gt;buf[len] != 'Z';len--) { c = s-&gt;buf[len]; /*Tool should detect this line as error*/ /* Stack Under RUN error */ /*if (s-&gt;buf[len] == '\0') break;*/ } }</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
